--- a/Template Import/Templates OU W Draft.xlsx
+++ b/Template Import/Templates OU W Draft.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB4440-4EF7-459A-9D54-F24CFBD81868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C562094-08AE-425A-92B0-A05AF057F8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{27F1575E-948A-46A9-9149-2F5AC0CC7443}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{27F1575E-948A-46A9-9149-2F5AC0CC7443}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
     <sheet name="L" sheetId="2" r:id="rId2"/>
+    <sheet name="VENDOR+PRODUCT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>DocNum</t>
   </si>
@@ -480,13 +481,106 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກສະຫມັກໃຈ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສູຂະພາບ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອຸບັດຕິເຫດສ່ວນບູກຄົນ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອຸດສາຫະກຳ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອື່ນໆ</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>Introducer fee - Marketing</t>
+  </si>
+  <si>
+    <t>ITF-Staff</t>
+  </si>
+  <si>
+    <t>Introducer fee - Staff</t>
+  </si>
+  <si>
+    <t>4033.01.03.01</t>
+  </si>
+  <si>
+    <t>4033.01.03.02</t>
+  </si>
+  <si>
+    <t>624.15.00</t>
+  </si>
+  <si>
+    <t>624.16.00</t>
+  </si>
+  <si>
+    <t>624.17.00</t>
+  </si>
+  <si>
+    <t>624.18.00</t>
+  </si>
+  <si>
+    <t>624.19.00</t>
+  </si>
+  <si>
+    <t>624.20.00</t>
+  </si>
+  <si>
+    <t>624.21.00</t>
+  </si>
+  <si>
+    <t>624.22.00</t>
+  </si>
+  <si>
+    <t>624.23.00</t>
+  </si>
+  <si>
+    <t>624.24.00</t>
+  </si>
+  <si>
+    <t>624.25.00</t>
+  </si>
+  <si>
+    <t>624.26.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,6 +633,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -603,7 +710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -624,6 +731,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -959,23 +1067,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C06EE4-FCF4-466B-965A-CCE33E48AF6D}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.4140625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.796875" style="6"/>
+    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1086,24 +1194,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD174DBA-CFD2-45FC-8EEA-DED8BCD6E15C}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
     <col min="11" max="11" width="20" style="6" customWidth="1"/>
-    <col min="12" max="12" width="14.59765625" style="6" customWidth="1"/>
-    <col min="13" max="16384" width="8.796875" style="6"/>
+    <col min="12" max="12" width="14.58203125" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1141,7 +1249,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1179,7 +1287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1213,4 +1321,144 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF55B2A-C239-496E-948A-143C4D5BC7C1}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="8.9140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.08203125" style="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F4" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F6" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Template Import/Templates OU W Draft.xlsx
+++ b/Template Import/Templates OU W Draft.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C562094-08AE-425A-92B0-A05AF057F8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B30278-37AD-403A-855B-4B20FF504AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{27F1575E-948A-46A9-9149-2F5AC0CC7443}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{27F1575E-948A-46A9-9149-2F5AC0CC7443}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
   <si>
     <t>DocNum</t>
   </si>
@@ -441,27 +441,15 @@
     <t>U_Channel</t>
   </si>
   <si>
-    <t>U_SLD_Claim</t>
-  </si>
-  <si>
-    <t>U_SLD_Ceded</t>
-  </si>
-  <si>
     <t>WhsCode</t>
   </si>
   <si>
     <t>VatSum</t>
   </si>
   <si>
-    <t>MOC0001</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
-    <t>IG00</t>
-  </si>
-  <si>
     <t>LAK</t>
   </si>
   <si>
@@ -574,6 +562,48 @@
   </si>
   <si>
     <t>624.26.00</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>OU W-Credit Life</t>
+  </si>
+  <si>
+    <t>OU W-Engineering</t>
+  </si>
+  <si>
+    <t>OU W-FIRE</t>
+  </si>
+  <si>
+    <t>OU W-Health</t>
+  </si>
+  <si>
+    <t>OU W-IAR</t>
+  </si>
+  <si>
+    <t>OU W-Marine</t>
+  </si>
+  <si>
+    <t>OU W-MISC</t>
+  </si>
+  <si>
+    <t>OU W-Motor compulsory</t>
+  </si>
+  <si>
+    <t>OU W-Motor Voluntary</t>
+  </si>
+  <si>
+    <t>OU W-PA</t>
+  </si>
+  <si>
+    <t>OU W-Property</t>
+  </si>
+  <si>
+    <t>OU W-TA</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -1067,23 +1097,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C06EE4-FCF4-466B-965A-CCE33E48AF6D}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="6"/>
+    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1139,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
@@ -1118,7 +1148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1144,7 +1174,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>8</v>
@@ -1153,7 +1183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1161,13 +1191,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G3" s="6">
         <v>111</v>
@@ -1182,7 +1212,7 @@
         <v>12</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1193,25 +1223,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD174DBA-CFD2-45FC-8EEA-DED8BCD6E15C}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.296875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="20" style="6" customWidth="1"/>
-    <col min="12" max="12" width="14.58203125" style="6" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="6"/>
+    <col min="7" max="7" width="19.796875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1242,14 +1270,8 @@
       <c r="J1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1285,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>18</v>
@@ -1272,7 +1294,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>21</v>
@@ -1280,19 +1302,13 @@
       <c r="J2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>27</v>
+      <c r="B3" t="s">
+        <v>72</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -1301,20 +1317,20 @@
         <v>1000000</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="G3" s="6">
         <v>1000000</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1326,135 +1342,175 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF55B2A-C239-496E-948A-143C4D5BC7C1}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="8.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.08203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.09765625" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A2" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A3" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F4" s="16" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F5" s="16" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G9" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F6" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F7" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F8" s="16" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G12" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F9" s="16" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F10" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F11" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F12" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F13" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Template Import/Templates OU W Draft.xlsx
+++ b/Template Import/Templates OU W Draft.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB4440-4EF7-459A-9D54-F24CFBD81868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B30278-37AD-403A-855B-4B20FF504AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{27F1575E-948A-46A9-9149-2F5AC0CC7443}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{27F1575E-948A-46A9-9149-2F5AC0CC7443}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
     <sheet name="L" sheetId="2" r:id="rId2"/>
+    <sheet name="VENDOR+PRODUCT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
   <si>
     <t>DocNum</t>
   </si>
@@ -440,27 +441,15 @@
     <t>U_Channel</t>
   </si>
   <si>
-    <t>U_SLD_Claim</t>
-  </si>
-  <si>
-    <t>U_SLD_Ceded</t>
-  </si>
-  <si>
     <t>WhsCode</t>
   </si>
   <si>
     <t>VatSum</t>
   </si>
   <si>
-    <t>MOC0001</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
-    <t>IG00</t>
-  </si>
-  <si>
     <t>LAK</t>
   </si>
   <si>
@@ -480,13 +469,148 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກສະຫມັກໃຈ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສູຂະພາບ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອຸບັດຕິເຫດສ່ວນບູກຄົນ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອຸດສາຫະກຳ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອື່ນໆ</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>Introducer fee - Marketing</t>
+  </si>
+  <si>
+    <t>ITF-Staff</t>
+  </si>
+  <si>
+    <t>Introducer fee - Staff</t>
+  </si>
+  <si>
+    <t>4033.01.03.01</t>
+  </si>
+  <si>
+    <t>4033.01.03.02</t>
+  </si>
+  <si>
+    <t>624.15.00</t>
+  </si>
+  <si>
+    <t>624.16.00</t>
+  </si>
+  <si>
+    <t>624.17.00</t>
+  </si>
+  <si>
+    <t>624.18.00</t>
+  </si>
+  <si>
+    <t>624.19.00</t>
+  </si>
+  <si>
+    <t>624.20.00</t>
+  </si>
+  <si>
+    <t>624.21.00</t>
+  </si>
+  <si>
+    <t>624.22.00</t>
+  </si>
+  <si>
+    <t>624.23.00</t>
+  </si>
+  <si>
+    <t>624.24.00</t>
+  </si>
+  <si>
+    <t>624.25.00</t>
+  </si>
+  <si>
+    <t>624.26.00</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>OU W-Credit Life</t>
+  </si>
+  <si>
+    <t>OU W-Engineering</t>
+  </si>
+  <si>
+    <t>OU W-FIRE</t>
+  </si>
+  <si>
+    <t>OU W-Health</t>
+  </si>
+  <si>
+    <t>OU W-IAR</t>
+  </si>
+  <si>
+    <t>OU W-Marine</t>
+  </si>
+  <si>
+    <t>OU W-MISC</t>
+  </si>
+  <si>
+    <t>OU W-Motor compulsory</t>
+  </si>
+  <si>
+    <t>OU W-Motor Voluntary</t>
+  </si>
+  <si>
+    <t>OU W-PA</t>
+  </si>
+  <si>
+    <t>OU W-Property</t>
+  </si>
+  <si>
+    <t>OU W-TA</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,6 +663,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -603,7 +740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -624,6 +761,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -959,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C06EE4-FCF4-466B-965A-CCE33E48AF6D}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
@@ -975,7 +1113,7 @@
     <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1001,7 +1139,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
@@ -1010,7 +1148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1174,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>8</v>
@@ -1045,7 +1183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1053,13 +1191,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G3" s="6">
         <v>111</v>
@@ -1074,7 +1212,7 @@
         <v>12</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1085,25 +1223,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD174DBA-CFD2-45FC-8EEA-DED8BCD6E15C}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="32.296875" style="6" customWidth="1"/>
     <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
     <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.796875" style="6" customWidth="1"/>
     <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="20" style="6" customWidth="1"/>
-    <col min="12" max="12" width="14.59765625" style="6" customWidth="1"/>
-    <col min="13" max="16384" width="8.796875" style="6"/>
+    <col min="11" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1134,14 +1270,8 @@
       <c r="J1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1155,7 +1285,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>18</v>
@@ -1164,7 +1294,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>21</v>
@@ -1172,19 +1302,13 @@
       <c r="J2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>27</v>
+      <c r="B3" t="s">
+        <v>72</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -1193,24 +1317,204 @@
         <v>1000000</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="G3" s="6">
         <v>1000000</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF55B2A-C239-496E-948A-143C4D5BC7C1}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.09765625" style="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="B1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A2" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A3" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>